--- a/docs/demo-data/GNDEC/GNDEC_2_CSE.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_2_CSE.xlsx
@@ -1012,7 +1012,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Er. Ekta Sethi</t>
+          <t>Prof. Ekta Sethi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Harleen Kohli</t>
+          <t>Prof. Harleen Kohli</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prof. Gurdeep Jindal</t>
+          <t>Dr. Gurdeep Jindal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Er. Amandeep Randhawa</t>
+          <t>Prof. Amandeep Randhawa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Er. Simranjit Mittal</t>
+          <t>Dr. Simranjit Mittal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dr. Baljit Cheema</t>
+          <t>Prof. Baljit Cheema</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Er. Sukhpreet Khanna</t>
+          <t>Prof. Sukhpreet Khanna</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Toor</t>
+          <t>Dr. Inderpreet Toor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dr. Daljeet Bedi</t>
+          <t>Prof. Daljeet Bedi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Garg</t>
+          <t>Prof. Prabhjot Garg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Er. Komal Bhalla</t>
+          <t>Dr. Komal Bhalla</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Anupam Bansal</t>
+          <t>Prof. Anupam Bansal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Er. Nidhi Ahluwalia</t>
+          <t>Dr. Nidhi Ahluwalia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dr. Varun Kohli</t>
+          <t>Prof. Varun Kohli</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Prof. Ekta Jindal</t>
+          <t>Dr. Ekta Jindal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Er. Tanvi Randhawa</t>
+          <t>Prof. Tanvi Randhawa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1947,7 +1947,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Er. Ekta Sethi</t>
+          <t>Prof. Ekta Sethi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2007,7 +2007,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Harleen Kohli</t>
+          <t>Prof. Harleen Kohli</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prof. Gurdeep Jindal</t>
+          <t>Dr. Gurdeep Jindal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Er. Amandeep Randhawa</t>
+          <t>Prof. Amandeep Randhawa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2082,7 +2082,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Er. Simranjit Mittal</t>
+          <t>Dr. Simranjit Mittal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dr. Baljit Cheema</t>
+          <t>Prof. Baljit Cheema</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Er. Sukhpreet Khanna</t>
+          <t>Prof. Sukhpreet Khanna</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2172,7 +2172,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Toor</t>
+          <t>Dr. Inderpreet Toor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dr. Daljeet Bedi</t>
+          <t>Prof. Daljeet Bedi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2202,7 +2202,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2217,7 +2217,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Garg</t>
+          <t>Prof. Prabhjot Garg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Er. Komal Bhalla</t>
+          <t>Dr. Komal Bhalla</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,7 +2277,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Anupam Bansal</t>
+          <t>Prof. Anupam Bansal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2307,7 +2307,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Er. Simranjit Mittal</t>
+          <t>Dr. Simranjit Mittal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2442,7 +2442,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2457,7 +2457,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Er. Nidhi Ahluwalia</t>
+          <t>Dr. Nidhi Ahluwalia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dr. Varun Kohli</t>
+          <t>Prof. Varun Kohli</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Prof. Ekta Jindal</t>
+          <t>Dr. Ekta Jindal</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Amandeep Kohli</t>
+          <t>Prof. Amandeep Kohli</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Amandeep Kohli</t>
+          <t>Prof. Amandeep Kohli</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Amandeep Kohli</t>
+          <t>Prof. Amandeep Kohli</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Amandeep Kohli</t>
+          <t>Prof. Amandeep Kohli</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Amandeep Kohli</t>
+          <t>Prof. Amandeep Kohli</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Amandeep Kohli</t>
+          <t>Prof. Amandeep Kohli</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Jagmeet Cheema</t>
+          <t>Prof. Jagmeet Cheema</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Jagmeet Cheema</t>
+          <t>Prof. Jagmeet Cheema</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dr. Ishpreet Bedi</t>
+          <t>Prof. Ishpreet Bedi</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dr. Ishpreet Bedi</t>
+          <t>Prof. Ishpreet Bedi</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dr. Ishpreet Bedi</t>
+          <t>Prof. Ishpreet Bedi</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prof. Gagandeep Anand</t>
+          <t>Dr. Gagandeep Anand</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prof. Gagandeep Anand</t>
+          <t>Dr. Gagandeep Anand</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Prof. Gagandeep Anand</t>
+          <t>Dr. Gagandeep Anand</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Er. Nitin Bhalla</t>
+          <t>Dr. Nitin Bhalla</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Er. Nitin Bhalla</t>
+          <t>Dr. Nitin Bhalla</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Er. Nitin Bhalla</t>
+          <t>Dr. Nitin Bhalla</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Er. Nitin Bhalla</t>
+          <t>Dr. Nitin Bhalla</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Er. Meenu Gill</t>
+          <t>Prof. Meenu Gill</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Er. Meenu Gill</t>
+          <t>Prof. Meenu Gill</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Prof. Varun Chopra</t>
+          <t>Dr. Varun Chopra</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Er. Ekta Sethi</t>
+          <t>Prof. Ekta Sethi</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Er. Ekta Sethi</t>
+          <t>Prof. Ekta Sethi</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Er. Ekta Sethi</t>
+          <t>Prof. Ekta Sethi</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Er. Bhavna Ahluwalia</t>
+          <t>Dr. Bhavna Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dr. Harleen Kohli</t>
+          <t>Prof. Harleen Kohli</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dr. Harleen Kohli</t>
+          <t>Prof. Harleen Kohli</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dr. Harleen Kohli</t>
+          <t>Prof. Harleen Kohli</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Prof. Gurdeep Jindal</t>
+          <t>Dr. Gurdeep Jindal</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Prof. Gurdeep Jindal</t>
+          <t>Dr. Gurdeep Jindal</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Er. Amandeep Randhawa</t>
+          <t>Prof. Amandeep Randhawa</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Er. Simranjit Mittal</t>
+          <t>Dr. Simranjit Mittal</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Er. Simranjit Mittal</t>
+          <t>Dr. Simranjit Mittal</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dr. Baljit Cheema</t>
+          <t>Prof. Baljit Cheema</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Prof. Ravneet Mann</t>
+          <t>Dr. Ravneet Mann</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Er. Sukhpreet Khanna</t>
+          <t>Prof. Sukhpreet Khanna</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Er. Sukhpreet Khanna</t>
+          <t>Prof. Sukhpreet Khanna</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Er. Sukhpreet Khanna</t>
+          <t>Prof. Sukhpreet Khanna</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Toor</t>
+          <t>Dr. Inderpreet Toor</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Toor</t>
+          <t>Dr. Inderpreet Toor</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dr. Daljeet Bedi</t>
+          <t>Prof. Daljeet Bedi</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Prof. Charanjit Anand</t>
+          <t>Dr. Charanjit Anand</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Garg</t>
+          <t>Prof. Prabhjot Garg</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Garg</t>
+          <t>Prof. Prabhjot Garg</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Er. Prabhjot Garg</t>
+          <t>Prof. Prabhjot Garg</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Er. Komal Bhalla</t>
+          <t>Dr. Komal Bhalla</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Er. Komal Bhalla</t>
+          <t>Dr. Komal Bhalla</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Er. Komal Bhalla</t>
+          <t>Dr. Komal Bhalla</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Er. Komal Bhalla</t>
+          <t>Dr. Komal Bhalla</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dr. Anupam Bansal</t>
+          <t>Prof. Anupam Bansal</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dr. Anupam Bansal</t>
+          <t>Prof. Anupam Bansal</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Kabir Grewal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Priya Bhatia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Uday Bansal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Rohan Jain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Sehaj Gupta</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Japneet Saini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Vihaan Verma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Jasleen Kapoor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Pranav Pannu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muskan Sandhu</t>
+          <t>Tanvi Dhillon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Noor Sidhu</t>
+          <t>Muskan Rana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hargun Chawla</t>
+          <t>Noor Mehta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sukhmani Aulakh</t>
+          <t>Hargun Aulakh</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ishaan Rana</t>
+          <t>Sukhmani Kaur</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nikita Pannu</t>
+          <t>Ishaan Chawla</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Simran Verma</t>
+          <t>Nikita Gill</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Gupta</t>
+          <t>Simran Sidhu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mehakpreet Bansal</t>
+          <t>Karan Malhi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gurnoor Grewal</t>
+          <t>Mehakpreet Sandhu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajbir Bedi</t>
+          <t>Gurnoor Goyal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harleen Thind</t>
+          <t>Rajbir Arora</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Navjot Goyal</t>
+          <t>Harleen Thind</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sanya Malhi</t>
+          <t>Navjot Singh</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gurleen Gill</t>
+          <t>Sanya Bedi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jashan Kaur</t>
+          <t>Gurleen Gill</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fatehbir Mehta</t>
+          <t>Jashan Sidhu</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prabhleen Dhillon</t>
+          <t>Fatehbir Malhi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diya Kapoor</t>
+          <t>Prabhleen Sandhu</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Meher Saini</t>
+          <t>Diya Goyal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sahil Jain</t>
+          <t>Meher Arora</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aditi Bhatia</t>
+          <t>Sahil Thind</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ekamjot Sharma</t>
+          <t>Aditi Singh</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avneet Singh</t>
+          <t>Ekamjot Bedi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manjot Arora</t>
+          <t>Avneet Sharma</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arjun Sandhu</t>
+          <t>Manjot Grewal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manav Sidhu</t>
+          <t>Arjun Bhatia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Riya Chawla</t>
+          <t>Manav Bansal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zoya Aulakh</t>
+          <t>Riya Jain</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arshdeep Rana</t>
+          <t>Zoya Gupta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yuvraj Pannu</t>
+          <t>Arshdeep Saini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lovepreet Verma</t>
+          <t>Yuvraj Verma</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ananya Gupta</t>
+          <t>Lovepreet Kapoor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kavya Bansal</t>
+          <t>Ananya Pannu</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rahul Grewal</t>
+          <t>Kavya Dhillon</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vansh Bedi</t>
+          <t>Rahul Rana</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sneha Thind</t>
+          <t>Vansh Mehta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Taranpreet Goyal</t>
+          <t>Sneha Aulakh</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Khushi Malhi</t>
+          <t>Taranpreet Kaur</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aarav Gill</t>
+          <t>Khushi Chawla</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Ananya Verma</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Kavya Kapoor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Rahul Pannu</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Vansh Dhillon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Sneha Rana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Taranpreet Mehta</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Khushi Aulakh</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Aarav Kaur</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Kabir Chawla</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Priya Gill</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Muskan Sandhu</t>
+          <t>Uday Sidhu</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Noor Sidhu</t>
+          <t>Rohan Malhi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hargun Chawla</t>
+          <t>Sehaj Sandhu</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sukhmani Aulakh</t>
+          <t>Japneet Goyal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ishaan Rana</t>
+          <t>Vihaan Arora</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nikita Pannu</t>
+          <t>Jasleen Thind</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Simran Verma</t>
+          <t>Pranav Singh</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Karan Gupta</t>
+          <t>Tanvi Bedi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mehakpreet Bansal</t>
+          <t>Muskan Sharma</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gurnoor Grewal</t>
+          <t>Noor Grewal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rajbir Bedi</t>
+          <t>Hargun Bhatia</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Harleen Thind</t>
+          <t>Sukhmani Bansal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Navjot Goyal</t>
+          <t>Ishaan Jain</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sanya Malhi</t>
+          <t>Nikita Gupta</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gurleen Gill</t>
+          <t>Simran Saini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jashan Kaur</t>
+          <t>Karan Singh</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fatehbir Mehta</t>
+          <t>Mehakpreet Bedi</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prabhleen Dhillon</t>
+          <t>Gurnoor Sharma</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Diya Kapoor</t>
+          <t>Rajbir Grewal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Meher Saini</t>
+          <t>Harleen Bhatia</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sahil Jain</t>
+          <t>Navjot Bansal</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Aditi Bhatia</t>
+          <t>Sanya Jain</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ekamjot Sharma</t>
+          <t>Gurleen Gupta</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Avneet Singh</t>
+          <t>Jashan Saini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Manjot Arora</t>
+          <t>Fatehbir Verma</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arjun Sandhu</t>
+          <t>Prabhleen Kapoor</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Manav Sidhu</t>
+          <t>Diya Pannu</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Riya Chawla</t>
+          <t>Meher Dhillon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zoya Aulakh</t>
+          <t>Sahil Rana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Arshdeep Rana</t>
+          <t>Aditi Mehta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Yuvraj Pannu</t>
+          <t>Ekamjot Aulakh</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lovepreet Verma</t>
+          <t>Avneet Kaur</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ananya Gupta</t>
+          <t>Manjot Chawla</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kavya Bansal</t>
+          <t>Arjun Gill</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rahul Grewal</t>
+          <t>Manav Sidhu</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vansh Bedi</t>
+          <t>Riya Malhi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sneha Thind</t>
+          <t>Zoya Sandhu</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Taranpreet Goyal</t>
+          <t>Arshdeep Goyal</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Khushi Malhi</t>
+          <t>Yuvraj Arora</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Aarav Gill</t>
+          <t>Lovepreet Thind</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Arjun Kaur</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Manav Chawla</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Riya Gill</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Zoya Sidhu</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Arshdeep Malhi</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Yuvraj Sandhu</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Lovepreet Goyal</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Ananya Arora</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Kavya Thind</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Rahul Singh</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Muskan Sandhu</t>
+          <t>Vansh Bedi</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Noor Sidhu</t>
+          <t>Sneha Sharma</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hargun Chawla</t>
+          <t>Taranpreet Grewal</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sukhmani Aulakh</t>
+          <t>Khushi Bhatia</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ishaan Rana</t>
+          <t>Aarav Bansal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nikita Pannu</t>
+          <t>Kabir Jain</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Simran Verma</t>
+          <t>Priya Gupta</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Karan Gupta</t>
+          <t>Uday Saini</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Rohan Verma</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Sehaj Kapoor</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Japneet Pannu</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Vihaan Dhillon</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Jasleen Rana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Pranav Mehta</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Tanvi Aulakh</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Muskan Gupta</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Noor Saini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Hargun Verma</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Sukhmani Kapoor</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Ishaan Pannu</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Nikita Dhillon</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Simran Rana</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Karan Mehta</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Mehakpreet Aulakh</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Gurnoor Kaur</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Rajbir Chawla</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Harleen Gill</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Navjot Sidhu</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Sanya Malhi</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Gurleen Sandhu</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Jashan Goyal</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Fatehbir Arora</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Prabhleen Thind</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Diya Singh</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Meher Bedi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Sahil Sharma</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Aditi Grewal</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Ekamjot Bhatia</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Avneet Bansal</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Manjot Jain</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Diya Arora</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Meher Thind</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Sahil Singh</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Aditi Bedi</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Ekamjot Sharma</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Avneet Grewal</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Manjot Bhatia</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Arjun Bansal</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Manav Jain</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Riya Gupta</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Zoya Saini</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Arshdeep Verma</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Yuvraj Kapoor</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Lovepreet Pannu</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Ananya Dhillon</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Kavya Rana</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Rahul Mehta</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Vansh Aulakh</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Sneha Kaur</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Taranpreet Chawla</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Khushi Gill</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Aarav Sidhu</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Kabir Malhi</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Priya Sandhu</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Uday Goyal</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Rohan Mehta</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Sehaj Aulakh</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Japneet Kaur</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Vihaan Chawla</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Jasleen Gill</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Pranav Sidhu</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Tanvi Malhi</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Muskan Sandhu</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Noor Goyal</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Hargun Arora</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Sukhmani Thind</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Ishaan Singh</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Nikita Bedi</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Simran Sharma</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Karan Grewal</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Mehakpreet Bhatia</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Gurnoor Bansal</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Rajbir Jain</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Harleen Gupta</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Navjot Saini</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Sanya Verma</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Gurleen Kapoor</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Jashan Pannu</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Fatehbir Dhillon</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Prabhleen Rana</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Harleen Bansal</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Navjot Jain</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Sanya Gupta</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Gurleen Saini</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Jashan Verma</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Fatehbir Kapoor</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Prabhleen Pannu</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Diya Dhillon</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Meher Rana</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Sahil Mehta</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Aditi Aulakh</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Ekamjot Kaur</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Avneet Chawla</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Manjot Gill</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Arjun Sidhu</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Manav Malhi</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Riya Sandhu</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Zoya Goyal</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Arshdeep Arora</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Yuvraj Thind</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Lovepreet Singh</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Ananya Bedi</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Kavya Sharma</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Rahul Grewal</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Vansh Bhatia</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Sneha Sandhu</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Taranpreet Goyal</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Khushi Arora</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Aarav Thind</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Kabir Singh</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Priya Bedi</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Uday Sharma</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Rohan Grewal</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Sehaj Bhatia</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Japneet Bansal</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Vihaan Jain</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Jasleen Gupta</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Pranav Saini</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Tanvi Verma</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Muskan Kapoor</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Noor Pannu</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Hargun Dhillon</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Sukhmani Rana</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Ishaan Mehta</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Nikita Aulakh</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Simran Kaur</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Karan Chawla</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Mehakpreet Gill</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Gurnoor Sidhu</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Rajbir Malhi</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Ishaan Dhillon</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Nikita Rana</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Simran Mehta</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Karan Aulakh</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Mehakpreet Kaur</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Gurnoor Chawla</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Rajbir Gill</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Harleen Sidhu</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Navjot Malhi</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Sanya Sandhu</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Gurleen Goyal</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Jashan Arora</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Fatehbir Thind</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Prabhleen Singh</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Diya Bedi</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Meher Sharma</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Sahil Grewal</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Aditi Bhatia</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Ekamjot Bansal</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Avneet Jain</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Manjot Gupta</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Arjun Saini</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Manav Verma</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Riya Kapoor</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Zoya Pannu</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Arshdeep Grewal</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Yuvraj Bhatia</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Lovepreet Bansal</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Ananya Jain</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Kavya Gupta</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Rahul Saini</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Vansh Verma</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Sneha Kapoor</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Taranpreet Pannu</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Khushi Dhillon</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Aarav Rana</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Kabir Mehta</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Priya Aulakh</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Uday Kaur</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Rohan Chawla</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Sehaj Gill</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Japneet Sidhu</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Vihaan Malhi</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Jasleen Sandhu</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Pranav Goyal</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Tanvi Arora</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Muskan Thind</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Noor Singh</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Hargun Bedi</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Sukhmani Sharma</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Jasleen Sidhu</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Pranav Malhi</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Tanvi Sandhu</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Muskan Goyal</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Noor Arora</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Hargun Thind</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Sukhmani Singh</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Ishaan Bedi</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Nikita Sharma</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Simran Grewal</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Karan Bhatia</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Mehakpreet Bansal</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Gurnoor Jain</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Rajbir Gupta</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Harleen Saini</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Navjot Verma</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Sanya Kapoor</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Gurleen Pannu</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Jashan Dhillon</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Fatehbir Rana</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Prabhleen Mehta</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Diya Aulakh</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Meher Kaur</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Sahil Chawla</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Aditi Gill</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Ekamjot Kapoor</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Avneet Pannu</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Manjot Dhillon</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Arjun Rana</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Manav Mehta</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Riya Aulakh</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Zoya Kaur</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Arshdeep Chawla</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Yuvraj Gill</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Lovepreet Sidhu</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Ananya Malhi</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Kavya Sandhu</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Rahul Goyal</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Vansh Arora</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Sneha Thind</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Taranpreet Singh</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Khushi Bedi</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Kabir Grewal</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Priya Bhatia</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Uday Bansal</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Rohan Jain</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Sehaj Gupta</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Japneet Saini</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Vihaan Verma</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Kabir Bedi</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Uday Grewal</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Rohan Bhatia</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Sehaj Bansal</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Japneet Jain</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Vihaan Gupta</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Jasleen Saini</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Pranav Verma</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Tanvi Kapoor</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Muskan Pannu</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Noor Dhillon</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Hargun Rana</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Sukhmani Mehta</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Ishaan Aulakh</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Nikita Kaur</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Simran Chawla</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Karan Gill</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Mehakpreet Sidhu</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Gurnoor Malhi</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Rajbir Sandhu</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Harleen Goyal</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Navjot Arora</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Sanya Thind</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Gurleen Singh</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Jashan Chawla</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Fatehbir Gill</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Prabhleen Sidhu</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Diya Malhi</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Meher Sandhu</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Sahil Goyal</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Aditi Arora</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Ekamjot Thind</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Avneet Singh</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Manjot Bedi</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Arjun Sharma</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Manav Grewal</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Riya Bhatia</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Zoya Bansal</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Arshdeep Jain</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Yuvraj Gupta</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Lovepreet Saini</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Ananya Verma</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Kavya Kapoor</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Rahul Pannu</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Vansh Dhillon</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Sneha Rana</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Taranpreet Mehta</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Khushi Aulakh</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Aarav Kaur</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Kavya Saini</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Rahul Verma</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Vansh Kapoor</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Sneha Pannu</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Taranpreet Dhillon</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Khushi Rana</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Aarav Mehta</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Kabir Aulakh</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Priya Kaur</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Uday Chawla</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Rohan Gill</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Sehaj Sidhu</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Japneet Malhi</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Vihaan Sandhu</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Jasleen Goyal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Pranav Arora</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Tanvi Thind</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Muskan Singh</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Noor Bedi</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Hargun Sharma</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Sukhmani Grewal</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Ishaan Bhatia</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Nikita Bansal</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Simran Jain</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Karan Gupta</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Mehakpreet Thind</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Gurnoor Singh</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Rajbir Bedi</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Harleen Sharma</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Navjot Grewal</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Sanya Bhatia</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Gurleen Bansal</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Jashan Jain</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Fatehbir Gupta</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Prabhleen Saini</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Diya Verma</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Meher Kapoor</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Sahil Pannu</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Aditi Dhillon</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Ekamjot Rana</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Avneet Mehta</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Manjot Aulakh</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Arjun Kaur</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Manav Chawla</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Riya Gill</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Zoya Sidhu</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Arshdeep Malhi</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Yuvraj Sandhu</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Lovepreet Goyal</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Ananya Arora</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Manav Aulakh</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Riya Kaur</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Zoya Chawla</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Arshdeep Gill</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Yuvraj Sidhu</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Lovepreet Malhi</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Ananya Sandhu</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Kavya Goyal</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Rahul Arora</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Vansh Thind</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Sneha Singh</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Taranpreet Bedi</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -18156,7 +18156,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Khushi Sharma</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Aarav Grewal</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Kabir Bhatia</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Priya Bansal</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Uday Jain</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Rohan Gupta</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Sehaj Saini</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Japneet Verma</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Vihaan Kapoor</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Jasleen Pannu</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Pranav Dhillon</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Tanvi Rana</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Muskan Mehta</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Noor Jain</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Hargun Gupta</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Sukhmani Saini</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Ishaan Verma</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Nikita Kapoor</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Simran Pannu</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Karan Dhillon</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Mehakpreet Rana</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Gurnoor Mehta</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Rajbir Aulakh</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Harleen Kaur</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Navjot Chawla</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Sanya Gill</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Gurleen Sidhu</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Jashan Malhi</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Fatehbir Sandhu</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Prabhleen Goyal</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Diya Arora</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Meher Thind</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Sahil Singh</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Aditi Bedi</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Ekamjot Sharma</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Avneet Grewal</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Manjot Bhatia</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Arjun Bansal</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Meher Goyal</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Sahil Arora</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Aditi Thind</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Ekamjot Singh</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Avneet Bedi</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -19317,7 +19317,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Manjot Sharma</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Arjun Grewal</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Manav Bhatia</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Riya Bansal</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Zoya Jain</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Arshdeep Gupta</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Yuvraj Saini</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Lovepreet Verma</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Ananya Kapoor</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Kavya Pannu</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Rahul Dhillon</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Vansh Rana</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Sneha Mehta</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Taranpreet Aulakh</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Khushi Kaur</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Aarav Chawla</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Kabir Gill</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Priya Sidhu</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Uday Malhi</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Rohan Sandhu</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Sehaj Rana</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Japneet Mehta</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Vihaan Aulakh</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Jasleen Kaur</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Pranav Chawla</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Tanvi Gill</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Muskan Sidhu</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -20046,7 +20046,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Noor Malhi</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Hargun Sandhu</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Sukhmani Goyal</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Ishaan Arora</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Nikita Thind</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Simran Singh</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Karan Bedi</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Mehakpreet Sharma</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Gurnoor Grewal</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Rajbir Bhatia</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Harleen Bansal</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Navjot Jain</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Sanya Gupta</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Gurleen Saini</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Jashan Verma</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Fatehbir Kapoor</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Prabhleen Pannu</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Diya Dhillon</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Navjot Bhatia</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -20559,7 +20559,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Sanya Bansal</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Gurleen Jain</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Jashan Gupta</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Fatehbir Saini</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Prabhleen Verma</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Diya Kapoor</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Meher Pannu</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Sahil Dhillon</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Aditi Rana</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Ekamjot Mehta</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Avneet Aulakh</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Manjot Kaur</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Arjun Chawla</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Manav Gill</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Riya Sidhu</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -20964,7 +20964,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Zoya Malhi</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Arshdeep Sandhu</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Yuvraj Goyal</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Lovepreet Arora</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Ananya Thind</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Kavya Singh</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Rahul Bedi</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Vansh Sharma</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Sneha Grewal</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Taranpreet Malhi</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Khushi Sandhu</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -21261,7 +21261,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Aarav Goyal</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Kabir Arora</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -21315,7 +21315,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Priya Thind</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Uday Singh</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Rohan Bedi</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Sehaj Sharma</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Japneet Grewal</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Vihaan Bhatia</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Jasleen Bansal</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Pranav Jain</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Tanvi Gupta</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Muskan Saini</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -21585,7 +21585,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Noor Verma</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Hargun Kapoor</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Sukhmani Pannu</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Ishaan Dhillon</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Nikita Rana</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Simran Mehta</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Karan Aulakh</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Mehakpreet Kaur</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Gurnoor Chawla</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Rajbir Gill</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Harleen Sidhu</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Nikita Pannu</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Simran Dhillon</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Karan Rana</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Mehakpreet Mehta</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Gurnoor Aulakh</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Rajbir Kaur</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Harleen Chawla</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Navjot Gill</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Sanya Sidhu</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -22125,7 +22125,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Gurleen Malhi</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Jashan Sandhu</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Fatehbir Goyal</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Prabhleen Arora</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Diya Thind</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Meher Singh</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Sahil Bedi</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Aditi Sharma</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Ekamjot Grewal</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Avneet Bhatia</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Manjot Bansal</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Arjun Jain</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -22449,7 +22449,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Manav Gupta</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Riya Saini</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Zoya Verma</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -22530,7 +22530,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Arshdeep Kapoor</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Yuvraj Sharma</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Lovepreet Grewal</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Ananya Bhatia</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Kavya Bansal</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Rahul Jain</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Vansh Gupta</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Sneha Saini</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Taranpreet Verma</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Khushi Kapoor</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Aarav Pannu</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Kabir Dhillon</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Priya Rana</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Uday Mehta</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Rohan Aulakh</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Sehaj Kaur</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Japneet Chawla</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Vihaan Gill</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Jasleen Sidhu</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Pranav Malhi</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Tanvi Sandhu</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Muskan Goyal</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -23124,7 +23124,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Noor Arora</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Hargun Thind</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Sukhmani Singh</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Ishaan Bedi</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -23232,7 +23232,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Pranav Gill</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Tanvi Sidhu</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">

--- a/docs/demo-data/GNDEC/GNDEC_2_CSE.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_2_CSE.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -472,178 +472,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>then CSE, IT, ME and CE. Shared halls, the JPAL hour and the final-year CSE elective are set up by</t>
+          <t>then CSE, IT, ME and CE. Its file also has the lecture theatres, drawing halls and workshops of</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>the College Admin (they are already in the built-in GNDEC demo college).</t>
+          <t>first year. Not in the files: the JPAL hour and the final-year CSE elective (they need a student list</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>per group; they are in the built-in GNDEC demo college).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Timetabl.ai: one department's data</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Rows are checked before anything is saved; problems are shown row by row. A '*' marks a required column.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sections: one row per section (a group of students who always sit together).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab batches: how the section splits for labs, e.g. 'A1:30, A2:30' (name:students). Empty = whole section.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Teachers: one row per teacher of the department.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Name, Email (their login), Shifts (one or more shift names, comma separated), Max periods per day (default 5).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Subjects: one row per subject the department teaches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab equipment: what the lab room must have, e.g. computers. It must match a lab room's Equipment.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Can teach: which subjects each teacher can teach. Preference 1 = first choice, 2 = could also teach it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Used for teacher suggestions and to find a substitute when a teacher is on leave.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Classes: one row per class. Subject code, Sections (several separated by commas = one combined class),</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">  once that department's file is uploaded: upload Applied Sciences first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Rooms: rooms this department owns. Type: Lecture, Lab or Seminar. Seats. Equipment for labs.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shared halls (lecture theatres, seminar hall, drawing halls, workshops) are added by the College Admin in Setup.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rooms every department may use (e.g. a seminar hall) are added by the College Admin in Setup as shared rooms.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>rules and shared rooms. The College Admin sets those in Setup.</t>
         </is>

--- a/docs/demo-data/GNDEC/GNDEC_2_CSE.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_2_CSE.xlsx
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2615001@gndec.demo</t>
+          <t>2615001@gndec.test</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2615002@gndec.demo</t>
+          <t>2615002@gndec.test</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2615003@gndec.demo</t>
+          <t>2615003@gndec.test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2615004@gndec.demo</t>
+          <t>2615004@gndec.test</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2615005@gndec.demo</t>
+          <t>2615005@gndec.test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2615006@gndec.demo</t>
+          <t>2615006@gndec.test</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2615007@gndec.demo</t>
+          <t>2615007@gndec.test</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2615008@gndec.demo</t>
+          <t>2615008@gndec.test</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2615009@gndec.demo</t>
+          <t>2615009@gndec.test</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2615010@gndec.demo</t>
+          <t>2615010@gndec.test</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2615011@gndec.demo</t>
+          <t>2615011@gndec.test</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2615012@gndec.demo</t>
+          <t>2615012@gndec.test</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2615013@gndec.demo</t>
+          <t>2615013@gndec.test</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2615014@gndec.demo</t>
+          <t>2615014@gndec.test</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2615015@gndec.demo</t>
+          <t>2615015@gndec.test</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2615016@gndec.demo</t>
+          <t>2615016@gndec.test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2615017@gndec.demo</t>
+          <t>2615017@gndec.test</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2615018@gndec.demo</t>
+          <t>2615018@gndec.test</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2615019@gndec.demo</t>
+          <t>2615019@gndec.test</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2615020@gndec.demo</t>
+          <t>2615020@gndec.test</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2615021@gndec.demo</t>
+          <t>2615021@gndec.test</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2615022@gndec.demo</t>
+          <t>2615022@gndec.test</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2615023@gndec.demo</t>
+          <t>2615023@gndec.test</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2615024@gndec.demo</t>
+          <t>2615024@gndec.test</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2615025@gndec.demo</t>
+          <t>2615025@gndec.test</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2615026@gndec.demo</t>
+          <t>2615026@gndec.test</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2615027@gndec.demo</t>
+          <t>2615027@gndec.test</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2615028@gndec.demo</t>
+          <t>2615028@gndec.test</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2615029@gndec.demo</t>
+          <t>2615029@gndec.test</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2615030@gndec.demo</t>
+          <t>2615030@gndec.test</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2615031@gndec.demo</t>
+          <t>2615031@gndec.test</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2615032@gndec.demo</t>
+          <t>2615032@gndec.test</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2615033@gndec.demo</t>
+          <t>2615033@gndec.test</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2615034@gndec.demo</t>
+          <t>2615034@gndec.test</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2615035@gndec.demo</t>
+          <t>2615035@gndec.test</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2615036@gndec.demo</t>
+          <t>2615036@gndec.test</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2615037@gndec.demo</t>
+          <t>2615037@gndec.test</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2615038@gndec.demo</t>
+          <t>2615038@gndec.test</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2615039@gndec.demo</t>
+          <t>2615039@gndec.test</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2615040@gndec.demo</t>
+          <t>2615040@gndec.test</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2615041@gndec.demo</t>
+          <t>2615041@gndec.test</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2615042@gndec.demo</t>
+          <t>2615042@gndec.test</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2615043@gndec.demo</t>
+          <t>2615043@gndec.test</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2615044@gndec.demo</t>
+          <t>2615044@gndec.test</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2615045@gndec.demo</t>
+          <t>2615045@gndec.test</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2615046@gndec.demo</t>
+          <t>2615046@gndec.test</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2615047@gndec.demo</t>
+          <t>2615047@gndec.test</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2615048@gndec.demo</t>
+          <t>2615048@gndec.test</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2615049@gndec.demo</t>
+          <t>2615049@gndec.test</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2615050@gndec.demo</t>
+          <t>2615050@gndec.test</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2615051@gndec.demo</t>
+          <t>2615051@gndec.test</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2615052@gndec.demo</t>
+          <t>2615052@gndec.test</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2615053@gndec.demo</t>
+          <t>2615053@gndec.test</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2615054@gndec.demo</t>
+          <t>2615054@gndec.test</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2615055@gndec.demo</t>
+          <t>2615055@gndec.test</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2615056@gndec.demo</t>
+          <t>2615056@gndec.test</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2615057@gndec.demo</t>
+          <t>2615057@gndec.test</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2615058@gndec.demo</t>
+          <t>2615058@gndec.test</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2615059@gndec.demo</t>
+          <t>2615059@gndec.test</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2615060@gndec.demo</t>
+          <t>2615060@gndec.test</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2615061@gndec.demo</t>
+          <t>2615061@gndec.test</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2615062@gndec.demo</t>
+          <t>2615062@gndec.test</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2615063@gndec.demo</t>
+          <t>2615063@gndec.test</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2615064@gndec.demo</t>
+          <t>2615064@gndec.test</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2615065@gndec.demo</t>
+          <t>2615065@gndec.test</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2615066@gndec.demo</t>
+          <t>2615066@gndec.test</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2615067@gndec.demo</t>
+          <t>2615067@gndec.test</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2615068@gndec.demo</t>
+          <t>2615068@gndec.test</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2615069@gndec.demo</t>
+          <t>2615069@gndec.test</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2615070@gndec.demo</t>
+          <t>2615070@gndec.test</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2615071@gndec.demo</t>
+          <t>2615071@gndec.test</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2615072@gndec.demo</t>
+          <t>2615072@gndec.test</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2615073@gndec.demo</t>
+          <t>2615073@gndec.test</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2615074@gndec.demo</t>
+          <t>2615074@gndec.test</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2615075@gndec.demo</t>
+          <t>2615075@gndec.test</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2615076@gndec.demo</t>
+          <t>2615076@gndec.test</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2615077@gndec.demo</t>
+          <t>2615077@gndec.test</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2615078@gndec.demo</t>
+          <t>2615078@gndec.test</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2615079@gndec.demo</t>
+          <t>2615079@gndec.test</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2615080@gndec.demo</t>
+          <t>2615080@gndec.test</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2615081@gndec.demo</t>
+          <t>2615081@gndec.test</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2615082@gndec.demo</t>
+          <t>2615082@gndec.test</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2615083@gndec.demo</t>
+          <t>2615083@gndec.test</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2615084@gndec.demo</t>
+          <t>2615084@gndec.test</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2615085@gndec.demo</t>
+          <t>2615085@gndec.test</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2615086@gndec.demo</t>
+          <t>2615086@gndec.test</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2615087@gndec.demo</t>
+          <t>2615087@gndec.test</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2615088@gndec.demo</t>
+          <t>2615088@gndec.test</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2615089@gndec.demo</t>
+          <t>2615089@gndec.test</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2615090@gndec.demo</t>
+          <t>2615090@gndec.test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2615091@gndec.demo</t>
+          <t>2615091@gndec.test</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2615092@gndec.demo</t>
+          <t>2615092@gndec.test</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2615093@gndec.demo</t>
+          <t>2615093@gndec.test</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2615094@gndec.demo</t>
+          <t>2615094@gndec.test</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2615095@gndec.demo</t>
+          <t>2615095@gndec.test</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2615096@gndec.demo</t>
+          <t>2615096@gndec.test</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2615097@gndec.demo</t>
+          <t>2615097@gndec.test</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2615098@gndec.demo</t>
+          <t>2615098@gndec.test</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2615099@gndec.demo</t>
+          <t>2615099@gndec.test</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2615100@gndec.demo</t>
+          <t>2615100@gndec.test</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2615101@gndec.demo</t>
+          <t>2615101@gndec.test</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2615102@gndec.demo</t>
+          <t>2615102@gndec.test</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2615103@gndec.demo</t>
+          <t>2615103@gndec.test</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2615104@gndec.demo</t>
+          <t>2615104@gndec.test</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2615105@gndec.demo</t>
+          <t>2615105@gndec.test</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2615106@gndec.demo</t>
+          <t>2615106@gndec.test</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2615107@gndec.demo</t>
+          <t>2615107@gndec.test</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2615108@gndec.demo</t>
+          <t>2615108@gndec.test</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2615109@gndec.demo</t>
+          <t>2615109@gndec.test</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2615110@gndec.demo</t>
+          <t>2615110@gndec.test</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2615111@gndec.demo</t>
+          <t>2615111@gndec.test</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2615112@gndec.demo</t>
+          <t>2615112@gndec.test</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2615113@gndec.demo</t>
+          <t>2615113@gndec.test</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2615114@gndec.demo</t>
+          <t>2615114@gndec.test</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2615115@gndec.demo</t>
+          <t>2615115@gndec.test</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2615116@gndec.demo</t>
+          <t>2615116@gndec.test</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2615117@gndec.demo</t>
+          <t>2615117@gndec.test</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2615118@gndec.demo</t>
+          <t>2615118@gndec.test</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2515001@gndec.demo</t>
+          <t>2515001@gndec.test</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2515002@gndec.demo</t>
+          <t>2515002@gndec.test</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2515003@gndec.demo</t>
+          <t>2515003@gndec.test</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2515004@gndec.demo</t>
+          <t>2515004@gndec.test</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2515005@gndec.demo</t>
+          <t>2515005@gndec.test</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2515006@gndec.demo</t>
+          <t>2515006@gndec.test</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2515007@gndec.demo</t>
+          <t>2515007@gndec.test</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2515008@gndec.demo</t>
+          <t>2515008@gndec.test</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2515009@gndec.demo</t>
+          <t>2515009@gndec.test</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2515010@gndec.demo</t>
+          <t>2515010@gndec.test</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2515011@gndec.demo</t>
+          <t>2515011@gndec.test</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2515012@gndec.demo</t>
+          <t>2515012@gndec.test</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2515013@gndec.demo</t>
+          <t>2515013@gndec.test</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2515014@gndec.demo</t>
+          <t>2515014@gndec.test</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2515015@gndec.demo</t>
+          <t>2515015@gndec.test</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2515016@gndec.demo</t>
+          <t>2515016@gndec.test</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2515017@gndec.demo</t>
+          <t>2515017@gndec.test</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2515018@gndec.demo</t>
+          <t>2515018@gndec.test</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2515019@gndec.demo</t>
+          <t>2515019@gndec.test</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2515020@gndec.demo</t>
+          <t>2515020@gndec.test</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2515021@gndec.demo</t>
+          <t>2515021@gndec.test</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2515022@gndec.demo</t>
+          <t>2515022@gndec.test</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2515023@gndec.demo</t>
+          <t>2515023@gndec.test</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2515024@gndec.demo</t>
+          <t>2515024@gndec.test</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2515025@gndec.demo</t>
+          <t>2515025@gndec.test</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2515026@gndec.demo</t>
+          <t>2515026@gndec.test</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2515027@gndec.demo</t>
+          <t>2515027@gndec.test</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2515028@gndec.demo</t>
+          <t>2515028@gndec.test</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2515029@gndec.demo</t>
+          <t>2515029@gndec.test</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2515030@gndec.demo</t>
+          <t>2515030@gndec.test</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2515031@gndec.demo</t>
+          <t>2515031@gndec.test</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2515032@gndec.demo</t>
+          <t>2515032@gndec.test</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2515033@gndec.demo</t>
+          <t>2515033@gndec.test</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2515034@gndec.demo</t>
+          <t>2515034@gndec.test</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2515035@gndec.demo</t>
+          <t>2515035@gndec.test</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2515036@gndec.demo</t>
+          <t>2515036@gndec.test</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2515037@gndec.demo</t>
+          <t>2515037@gndec.test</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2515038@gndec.demo</t>
+          <t>2515038@gndec.test</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2515039@gndec.demo</t>
+          <t>2515039@gndec.test</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2515040@gndec.demo</t>
+          <t>2515040@gndec.test</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2515041@gndec.demo</t>
+          <t>2515041@gndec.test</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2515042@gndec.demo</t>
+          <t>2515042@gndec.test</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2515043@gndec.demo</t>
+          <t>2515043@gndec.test</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2515044@gndec.demo</t>
+          <t>2515044@gndec.test</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2515045@gndec.demo</t>
+          <t>2515045@gndec.test</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2515046@gndec.demo</t>
+          <t>2515046@gndec.test</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2515047@gndec.demo</t>
+          <t>2515047@gndec.test</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2515048@gndec.demo</t>
+          <t>2515048@gndec.test</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2515049@gndec.demo</t>
+          <t>2515049@gndec.test</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2515050@gndec.demo</t>
+          <t>2515050@gndec.test</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2515051@gndec.demo</t>
+          <t>2515051@gndec.test</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2515052@gndec.demo</t>
+          <t>2515052@gndec.test</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2515053@gndec.demo</t>
+          <t>2515053@gndec.test</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2515054@gndec.demo</t>
+          <t>2515054@gndec.test</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2515055@gndec.demo</t>
+          <t>2515055@gndec.test</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2515056@gndec.demo</t>
+          <t>2515056@gndec.test</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2515057@gndec.demo</t>
+          <t>2515057@gndec.test</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2515058@gndec.demo</t>
+          <t>2515058@gndec.test</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2515059@gndec.demo</t>
+          <t>2515059@gndec.test</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2515060@gndec.demo</t>
+          <t>2515060@gndec.test</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2515061@gndec.demo</t>
+          <t>2515061@gndec.test</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2515062@gndec.demo</t>
+          <t>2515062@gndec.test</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2515063@gndec.demo</t>
+          <t>2515063@gndec.test</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2515064@gndec.demo</t>
+          <t>2515064@gndec.test</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2515065@gndec.demo</t>
+          <t>2515065@gndec.test</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2515066@gndec.demo</t>
+          <t>2515066@gndec.test</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2515067@gndec.demo</t>
+          <t>2515067@gndec.test</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2515068@gndec.demo</t>
+          <t>2515068@gndec.test</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2515069@gndec.demo</t>
+          <t>2515069@gndec.test</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2515070@gndec.demo</t>
+          <t>2515070@gndec.test</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2515071@gndec.demo</t>
+          <t>2515071@gndec.test</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2515072@gndec.demo</t>
+          <t>2515072@gndec.test</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2515073@gndec.demo</t>
+          <t>2515073@gndec.test</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2515074@gndec.demo</t>
+          <t>2515074@gndec.test</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2515075@gndec.demo</t>
+          <t>2515075@gndec.test</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2515076@gndec.demo</t>
+          <t>2515076@gndec.test</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2515077@gndec.demo</t>
+          <t>2515077@gndec.test</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2515078@gndec.demo</t>
+          <t>2515078@gndec.test</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2515079@gndec.demo</t>
+          <t>2515079@gndec.test</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2515080@gndec.demo</t>
+          <t>2515080@gndec.test</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2515081@gndec.demo</t>
+          <t>2515081@gndec.test</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2515082@gndec.demo</t>
+          <t>2515082@gndec.test</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2515083@gndec.demo</t>
+          <t>2515083@gndec.test</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2515084@gndec.demo</t>
+          <t>2515084@gndec.test</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2515085@gndec.demo</t>
+          <t>2515085@gndec.test</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2515086@gndec.demo</t>
+          <t>2515086@gndec.test</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2515087@gndec.demo</t>
+          <t>2515087@gndec.test</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2515088@gndec.demo</t>
+          <t>2515088@gndec.test</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2515089@gndec.demo</t>
+          <t>2515089@gndec.test</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2515090@gndec.demo</t>
+          <t>2515090@gndec.test</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2515091@gndec.demo</t>
+          <t>2515091@gndec.test</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2515092@gndec.demo</t>
+          <t>2515092@gndec.test</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2515093@gndec.demo</t>
+          <t>2515093@gndec.test</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2515094@gndec.demo</t>
+          <t>2515094@gndec.test</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2515095@gndec.demo</t>
+          <t>2515095@gndec.test</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2515096@gndec.demo</t>
+          <t>2515096@gndec.test</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2515097@gndec.demo</t>
+          <t>2515097@gndec.test</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2515098@gndec.demo</t>
+          <t>2515098@gndec.test</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2515099@gndec.demo</t>
+          <t>2515099@gndec.test</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2515100@gndec.demo</t>
+          <t>2515100@gndec.test</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2515101@gndec.demo</t>
+          <t>2515101@gndec.test</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2515102@gndec.demo</t>
+          <t>2515102@gndec.test</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2515103@gndec.demo</t>
+          <t>2515103@gndec.test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2515104@gndec.demo</t>
+          <t>2515104@gndec.test</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2515105@gndec.demo</t>
+          <t>2515105@gndec.test</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2515106@gndec.demo</t>
+          <t>2515106@gndec.test</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2515107@gndec.demo</t>
+          <t>2515107@gndec.test</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2515108@gndec.demo</t>
+          <t>2515108@gndec.test</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2515109@gndec.demo</t>
+          <t>2515109@gndec.test</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2515110@gndec.demo</t>
+          <t>2515110@gndec.test</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2515111@gndec.demo</t>
+          <t>2515111@gndec.test</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2515112@gndec.demo</t>
+          <t>2515112@gndec.test</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2515113@gndec.demo</t>
+          <t>2515113@gndec.test</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2515114@gndec.demo</t>
+          <t>2515114@gndec.test</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2515115@gndec.demo</t>
+          <t>2515115@gndec.test</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2515116@gndec.demo</t>
+          <t>2515116@gndec.test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2515117@gndec.demo</t>
+          <t>2515117@gndec.test</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2515118@gndec.demo</t>
+          <t>2515118@gndec.test</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2515119@gndec.demo</t>
+          <t>2515119@gndec.test</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2515120@gndec.demo</t>
+          <t>2515120@gndec.test</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2515121@gndec.demo</t>
+          <t>2515121@gndec.test</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2515122@gndec.demo</t>
+          <t>2515122@gndec.test</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2515123@gndec.demo</t>
+          <t>2515123@gndec.test</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2515124@gndec.demo</t>
+          <t>2515124@gndec.test</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2515125@gndec.demo</t>
+          <t>2515125@gndec.test</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2515126@gndec.demo</t>
+          <t>2515126@gndec.test</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2515127@gndec.demo</t>
+          <t>2515127@gndec.test</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2515128@gndec.demo</t>
+          <t>2515128@gndec.test</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2515129@gndec.demo</t>
+          <t>2515129@gndec.test</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2515130@gndec.demo</t>
+          <t>2515130@gndec.test</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2515131@gndec.demo</t>
+          <t>2515131@gndec.test</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2515132@gndec.demo</t>
+          <t>2515132@gndec.test</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2515133@gndec.demo</t>
+          <t>2515133@gndec.test</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2515134@gndec.demo</t>
+          <t>2515134@gndec.test</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2515135@gndec.demo</t>
+          <t>2515135@gndec.test</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2515136@gndec.demo</t>
+          <t>2515136@gndec.test</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2515137@gndec.demo</t>
+          <t>2515137@gndec.test</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2515138@gndec.demo</t>
+          <t>2515138@gndec.test</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2515139@gndec.demo</t>
+          <t>2515139@gndec.test</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2515140@gndec.demo</t>
+          <t>2515140@gndec.test</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2515141@gndec.demo</t>
+          <t>2515141@gndec.test</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2515142@gndec.demo</t>
+          <t>2515142@gndec.test</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2515143@gndec.demo</t>
+          <t>2515143@gndec.test</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2515144@gndec.demo</t>
+          <t>2515144@gndec.test</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2515145@gndec.demo</t>
+          <t>2515145@gndec.test</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2515146@gndec.demo</t>
+          <t>2515146@gndec.test</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2515147@gndec.demo</t>
+          <t>2515147@gndec.test</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2515148@gndec.demo</t>
+          <t>2515148@gndec.test</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2515149@gndec.demo</t>
+          <t>2515149@gndec.test</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2515150@gndec.demo</t>
+          <t>2515150@gndec.test</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2515151@gndec.demo</t>
+          <t>2515151@gndec.test</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2515152@gndec.demo</t>
+          <t>2515152@gndec.test</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2515153@gndec.demo</t>
+          <t>2515153@gndec.test</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2515154@gndec.demo</t>
+          <t>2515154@gndec.test</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2515155@gndec.demo</t>
+          <t>2515155@gndec.test</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2515156@gndec.demo</t>
+          <t>2515156@gndec.test</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2515157@gndec.demo</t>
+          <t>2515157@gndec.test</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2515158@gndec.demo</t>
+          <t>2515158@gndec.test</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2515159@gndec.demo</t>
+          <t>2515159@gndec.test</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2515160@gndec.demo</t>
+          <t>2515160@gndec.test</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2515161@gndec.demo</t>
+          <t>2515161@gndec.test</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2515162@gndec.demo</t>
+          <t>2515162@gndec.test</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2515163@gndec.demo</t>
+          <t>2515163@gndec.test</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2515164@gndec.demo</t>
+          <t>2515164@gndec.test</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2515165@gndec.demo</t>
+          <t>2515165@gndec.test</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2515166@gndec.demo</t>
+          <t>2515166@gndec.test</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2515167@gndec.demo</t>
+          <t>2515167@gndec.test</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2515168@gndec.demo</t>
+          <t>2515168@gndec.test</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2515169@gndec.demo</t>
+          <t>2515169@gndec.test</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2515170@gndec.demo</t>
+          <t>2515170@gndec.test</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2515171@gndec.demo</t>
+          <t>2515171@gndec.test</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2515172@gndec.demo</t>
+          <t>2515172@gndec.test</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2515173@gndec.demo</t>
+          <t>2515173@gndec.test</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2515174@gndec.demo</t>
+          <t>2515174@gndec.test</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2515175@gndec.demo</t>
+          <t>2515175@gndec.test</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2515176@gndec.demo</t>
+          <t>2515176@gndec.test</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2515177@gndec.demo</t>
+          <t>2515177@gndec.test</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2515178@gndec.demo</t>
+          <t>2515178@gndec.test</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2415001@gndec.demo</t>
+          <t>2415001@gndec.test</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2415002@gndec.demo</t>
+          <t>2415002@gndec.test</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2415003@gndec.demo</t>
+          <t>2415003@gndec.test</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2415004@gndec.demo</t>
+          <t>2415004@gndec.test</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2415005@gndec.demo</t>
+          <t>2415005@gndec.test</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2415006@gndec.demo</t>
+          <t>2415006@gndec.test</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2415007@gndec.demo</t>
+          <t>2415007@gndec.test</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2415008@gndec.demo</t>
+          <t>2415008@gndec.test</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2415009@gndec.demo</t>
+          <t>2415009@gndec.test</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2415010@gndec.demo</t>
+          <t>2415010@gndec.test</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2415011@gndec.demo</t>
+          <t>2415011@gndec.test</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2415012@gndec.demo</t>
+          <t>2415012@gndec.test</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2415013@gndec.demo</t>
+          <t>2415013@gndec.test</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2415014@gndec.demo</t>
+          <t>2415014@gndec.test</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2415015@gndec.demo</t>
+          <t>2415015@gndec.test</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2415016@gndec.demo</t>
+          <t>2415016@gndec.test</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2415017@gndec.demo</t>
+          <t>2415017@gndec.test</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2415018@gndec.demo</t>
+          <t>2415018@gndec.test</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2415019@gndec.demo</t>
+          <t>2415019@gndec.test</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2415020@gndec.demo</t>
+          <t>2415020@gndec.test</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2415021@gndec.demo</t>
+          <t>2415021@gndec.test</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2415022@gndec.demo</t>
+          <t>2415022@gndec.test</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2415023@gndec.demo</t>
+          <t>2415023@gndec.test</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2415024@gndec.demo</t>
+          <t>2415024@gndec.test</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2415025@gndec.demo</t>
+          <t>2415025@gndec.test</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2415026@gndec.demo</t>
+          <t>2415026@gndec.test</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2415027@gndec.demo</t>
+          <t>2415027@gndec.test</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2415028@gndec.demo</t>
+          <t>2415028@gndec.test</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2415029@gndec.demo</t>
+          <t>2415029@gndec.test</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2415030@gndec.demo</t>
+          <t>2415030@gndec.test</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2415031@gndec.demo</t>
+          <t>2415031@gndec.test</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2415032@gndec.demo</t>
+          <t>2415032@gndec.test</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2415033@gndec.demo</t>
+          <t>2415033@gndec.test</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2415034@gndec.demo</t>
+          <t>2415034@gndec.test</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2415035@gndec.demo</t>
+          <t>2415035@gndec.test</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2415036@gndec.demo</t>
+          <t>2415036@gndec.test</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2415037@gndec.demo</t>
+          <t>2415037@gndec.test</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2415038@gndec.demo</t>
+          <t>2415038@gndec.test</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2415039@gndec.demo</t>
+          <t>2415039@gndec.test</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2415040@gndec.demo</t>
+          <t>2415040@gndec.test</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2415041@gndec.demo</t>
+          <t>2415041@gndec.test</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2415042@gndec.demo</t>
+          <t>2415042@gndec.test</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2415043@gndec.demo</t>
+          <t>2415043@gndec.test</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2415044@gndec.demo</t>
+          <t>2415044@gndec.test</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2415045@gndec.demo</t>
+          <t>2415045@gndec.test</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2415046@gndec.demo</t>
+          <t>2415046@gndec.test</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2415047@gndec.demo</t>
+          <t>2415047@gndec.test</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2415048@gndec.demo</t>
+          <t>2415048@gndec.test</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2415049@gndec.demo</t>
+          <t>2415049@gndec.test</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2415050@gndec.demo</t>
+          <t>2415050@gndec.test</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2415051@gndec.demo</t>
+          <t>2415051@gndec.test</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2415052@gndec.demo</t>
+          <t>2415052@gndec.test</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2415053@gndec.demo</t>
+          <t>2415053@gndec.test</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2415054@gndec.demo</t>
+          <t>2415054@gndec.test</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2415055@gndec.demo</t>
+          <t>2415055@gndec.test</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2415056@gndec.demo</t>
+          <t>2415056@gndec.test</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2415057@gndec.demo</t>
+          <t>2415057@gndec.test</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2415058@gndec.demo</t>
+          <t>2415058@gndec.test</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2415059@gndec.demo</t>
+          <t>2415059@gndec.test</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2415060@gndec.demo</t>
+          <t>2415060@gndec.test</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2415061@gndec.demo</t>
+          <t>2415061@gndec.test</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2415062@gndec.demo</t>
+          <t>2415062@gndec.test</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2415063@gndec.demo</t>
+          <t>2415063@gndec.test</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2415064@gndec.demo</t>
+          <t>2415064@gndec.test</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2415065@gndec.demo</t>
+          <t>2415065@gndec.test</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2415066@gndec.demo</t>
+          <t>2415066@gndec.test</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2415067@gndec.demo</t>
+          <t>2415067@gndec.test</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2415068@gndec.demo</t>
+          <t>2415068@gndec.test</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2415069@gndec.demo</t>
+          <t>2415069@gndec.test</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2415070@gndec.demo</t>
+          <t>2415070@gndec.test</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2415071@gndec.demo</t>
+          <t>2415071@gndec.test</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2415072@gndec.demo</t>
+          <t>2415072@gndec.test</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2415073@gndec.demo</t>
+          <t>2415073@gndec.test</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2415074@gndec.demo</t>
+          <t>2415074@gndec.test</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2415075@gndec.demo</t>
+          <t>2415075@gndec.test</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2415076@gndec.demo</t>
+          <t>2415076@gndec.test</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2415077@gndec.demo</t>
+          <t>2415077@gndec.test</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2415078@gndec.demo</t>
+          <t>2415078@gndec.test</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2415079@gndec.demo</t>
+          <t>2415079@gndec.test</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2415080@gndec.demo</t>
+          <t>2415080@gndec.test</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2415081@gndec.demo</t>
+          <t>2415081@gndec.test</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2415082@gndec.demo</t>
+          <t>2415082@gndec.test</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2415083@gndec.demo</t>
+          <t>2415083@gndec.test</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2415084@gndec.demo</t>
+          <t>2415084@gndec.test</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2415085@gndec.demo</t>
+          <t>2415085@gndec.test</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2415086@gndec.demo</t>
+          <t>2415086@gndec.test</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2415087@gndec.demo</t>
+          <t>2415087@gndec.test</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2415088@gndec.demo</t>
+          <t>2415088@gndec.test</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2415089@gndec.demo</t>
+          <t>2415089@gndec.test</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2415090@gndec.demo</t>
+          <t>2415090@gndec.test</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2415091@gndec.demo</t>
+          <t>2415091@gndec.test</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2415092@gndec.demo</t>
+          <t>2415092@gndec.test</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2415093@gndec.demo</t>
+          <t>2415093@gndec.test</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2415094@gndec.demo</t>
+          <t>2415094@gndec.test</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2415095@gndec.demo</t>
+          <t>2415095@gndec.test</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2415096@gndec.demo</t>
+          <t>2415096@gndec.test</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2415097@gndec.demo</t>
+          <t>2415097@gndec.test</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2415098@gndec.demo</t>
+          <t>2415098@gndec.test</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2415099@gndec.demo</t>
+          <t>2415099@gndec.test</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2415100@gndec.demo</t>
+          <t>2415100@gndec.test</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2415101@gndec.demo</t>
+          <t>2415101@gndec.test</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2415102@gndec.demo</t>
+          <t>2415102@gndec.test</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2415103@gndec.demo</t>
+          <t>2415103@gndec.test</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2415104@gndec.demo</t>
+          <t>2415104@gndec.test</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2415105@gndec.demo</t>
+          <t>2415105@gndec.test</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2415106@gndec.demo</t>
+          <t>2415106@gndec.test</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2415107@gndec.demo</t>
+          <t>2415107@gndec.test</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2415108@gndec.demo</t>
+          <t>2415108@gndec.test</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2415109@gndec.demo</t>
+          <t>2415109@gndec.test</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2415110@gndec.demo</t>
+          <t>2415110@gndec.test</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2415111@gndec.demo</t>
+          <t>2415111@gndec.test</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2415112@gndec.demo</t>
+          <t>2415112@gndec.test</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2415113@gndec.demo</t>
+          <t>2415113@gndec.test</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2415114@gndec.demo</t>
+          <t>2415114@gndec.test</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2415115@gndec.demo</t>
+          <t>2415115@gndec.test</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2415116@gndec.demo</t>
+          <t>2415116@gndec.test</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2415117@gndec.demo</t>
+          <t>2415117@gndec.test</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2415118@gndec.demo</t>
+          <t>2415118@gndec.test</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2415119@gndec.demo</t>
+          <t>2415119@gndec.test</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2415120@gndec.demo</t>
+          <t>2415120@gndec.test</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2415121@gndec.demo</t>
+          <t>2415121@gndec.test</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2415122@gndec.demo</t>
+          <t>2415122@gndec.test</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2415123@gndec.demo</t>
+          <t>2415123@gndec.test</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2415124@gndec.demo</t>
+          <t>2415124@gndec.test</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2415125@gndec.demo</t>
+          <t>2415125@gndec.test</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2415126@gndec.demo</t>
+          <t>2415126@gndec.test</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2415127@gndec.demo</t>
+          <t>2415127@gndec.test</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2415128@gndec.demo</t>
+          <t>2415128@gndec.test</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2415129@gndec.demo</t>
+          <t>2415129@gndec.test</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2415130@gndec.demo</t>
+          <t>2415130@gndec.test</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2415131@gndec.demo</t>
+          <t>2415131@gndec.test</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2415132@gndec.demo</t>
+          <t>2415132@gndec.test</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2415133@gndec.demo</t>
+          <t>2415133@gndec.test</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2415134@gndec.demo</t>
+          <t>2415134@gndec.test</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2415135@gndec.demo</t>
+          <t>2415135@gndec.test</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2415136@gndec.demo</t>
+          <t>2415136@gndec.test</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2415137@gndec.demo</t>
+          <t>2415137@gndec.test</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2415138@gndec.demo</t>
+          <t>2415138@gndec.test</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2415139@gndec.demo</t>
+          <t>2415139@gndec.test</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2415140@gndec.demo</t>
+          <t>2415140@gndec.test</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2415141@gndec.demo</t>
+          <t>2415141@gndec.test</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2415142@gndec.demo</t>
+          <t>2415142@gndec.test</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2415143@gndec.demo</t>
+          <t>2415143@gndec.test</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2415144@gndec.demo</t>
+          <t>2415144@gndec.test</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2415145@gndec.demo</t>
+          <t>2415145@gndec.test</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2415146@gndec.demo</t>
+          <t>2415146@gndec.test</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2415147@gndec.demo</t>
+          <t>2415147@gndec.test</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2415148@gndec.demo</t>
+          <t>2415148@gndec.test</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2415149@gndec.demo</t>
+          <t>2415149@gndec.test</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2415150@gndec.demo</t>
+          <t>2415150@gndec.test</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2415151@gndec.demo</t>
+          <t>2415151@gndec.test</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2415152@gndec.demo</t>
+          <t>2415152@gndec.test</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2415153@gndec.demo</t>
+          <t>2415153@gndec.test</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2415154@gndec.demo</t>
+          <t>2415154@gndec.test</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2415155@gndec.demo</t>
+          <t>2415155@gndec.test</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2415156@gndec.demo</t>
+          <t>2415156@gndec.test</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2415157@gndec.demo</t>
+          <t>2415157@gndec.test</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -17925,7 +17925,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2415158@gndec.demo</t>
+          <t>2415158@gndec.test</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2415159@gndec.demo</t>
+          <t>2415159@gndec.test</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2415160@gndec.demo</t>
+          <t>2415160@gndec.test</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2415161@gndec.demo</t>
+          <t>2415161@gndec.test</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2415162@gndec.demo</t>
+          <t>2415162@gndec.test</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2415163@gndec.demo</t>
+          <t>2415163@gndec.test</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2415164@gndec.demo</t>
+          <t>2415164@gndec.test</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2415165@gndec.demo</t>
+          <t>2415165@gndec.test</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2415166@gndec.demo</t>
+          <t>2415166@gndec.test</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2415167@gndec.demo</t>
+          <t>2415167@gndec.test</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2415168@gndec.demo</t>
+          <t>2415168@gndec.test</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2415169@gndec.demo</t>
+          <t>2415169@gndec.test</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2415170@gndec.demo</t>
+          <t>2415170@gndec.test</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2415171@gndec.demo</t>
+          <t>2415171@gndec.test</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2415172@gndec.demo</t>
+          <t>2415172@gndec.test</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2415173@gndec.demo</t>
+          <t>2415173@gndec.test</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2415174@gndec.demo</t>
+          <t>2415174@gndec.test</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2415175@gndec.demo</t>
+          <t>2415175@gndec.test</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2415176@gndec.demo</t>
+          <t>2415176@gndec.test</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2415177@gndec.demo</t>
+          <t>2415177@gndec.test</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2415178@gndec.demo</t>
+          <t>2415178@gndec.test</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2315001@gndec.demo</t>
+          <t>2315001@gndec.test</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2315002@gndec.demo</t>
+          <t>2315002@gndec.test</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2315003@gndec.demo</t>
+          <t>2315003@gndec.test</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2315004@gndec.demo</t>
+          <t>2315004@gndec.test</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2315005@gndec.demo</t>
+          <t>2315005@gndec.test</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2315006@gndec.demo</t>
+          <t>2315006@gndec.test</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2315007@gndec.demo</t>
+          <t>2315007@gndec.test</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2315008@gndec.demo</t>
+          <t>2315008@gndec.test</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2315009@gndec.demo</t>
+          <t>2315009@gndec.test</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2315010@gndec.demo</t>
+          <t>2315010@gndec.test</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2315011@gndec.demo</t>
+          <t>2315011@gndec.test</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2315012@gndec.demo</t>
+          <t>2315012@gndec.test</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2315013@gndec.demo</t>
+          <t>2315013@gndec.test</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2315014@gndec.demo</t>
+          <t>2315014@gndec.test</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2315015@gndec.demo</t>
+          <t>2315015@gndec.test</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2315016@gndec.demo</t>
+          <t>2315016@gndec.test</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2315017@gndec.demo</t>
+          <t>2315017@gndec.test</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2315018@gndec.demo</t>
+          <t>2315018@gndec.test</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2315019@gndec.demo</t>
+          <t>2315019@gndec.test</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -19005,7 +19005,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2315020@gndec.demo</t>
+          <t>2315020@gndec.test</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2315021@gndec.demo</t>
+          <t>2315021@gndec.test</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2315022@gndec.demo</t>
+          <t>2315022@gndec.test</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2315023@gndec.demo</t>
+          <t>2315023@gndec.test</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2315024@gndec.demo</t>
+          <t>2315024@gndec.test</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2315025@gndec.demo</t>
+          <t>2315025@gndec.test</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2315026@gndec.demo</t>
+          <t>2315026@gndec.test</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2315027@gndec.demo</t>
+          <t>2315027@gndec.test</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2315028@gndec.demo</t>
+          <t>2315028@gndec.test</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2315029@gndec.demo</t>
+          <t>2315029@gndec.test</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2315030@gndec.demo</t>
+          <t>2315030@gndec.test</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2315031@gndec.demo</t>
+          <t>2315031@gndec.test</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2315032@gndec.demo</t>
+          <t>2315032@gndec.test</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2315033@gndec.demo</t>
+          <t>2315033@gndec.test</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2315034@gndec.demo</t>
+          <t>2315034@gndec.test</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2315035@gndec.demo</t>
+          <t>2315035@gndec.test</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2315036@gndec.demo</t>
+          <t>2315036@gndec.test</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2315037@gndec.demo</t>
+          <t>2315037@gndec.test</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2315038@gndec.demo</t>
+          <t>2315038@gndec.test</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2315039@gndec.demo</t>
+          <t>2315039@gndec.test</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2315040@gndec.demo</t>
+          <t>2315040@gndec.test</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2315041@gndec.demo</t>
+          <t>2315041@gndec.test</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2315042@gndec.demo</t>
+          <t>2315042@gndec.test</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2315043@gndec.demo</t>
+          <t>2315043@gndec.test</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2315044@gndec.demo</t>
+          <t>2315044@gndec.test</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -19680,7 +19680,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2315045@gndec.demo</t>
+          <t>2315045@gndec.test</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2315046@gndec.demo</t>
+          <t>2315046@gndec.test</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2315047@gndec.demo</t>
+          <t>2315047@gndec.test</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2315048@gndec.demo</t>
+          <t>2315048@gndec.test</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2315049@gndec.demo</t>
+          <t>2315049@gndec.test</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2315050@gndec.demo</t>
+          <t>2315050@gndec.test</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2315051@gndec.demo</t>
+          <t>2315051@gndec.test</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2315052@gndec.demo</t>
+          <t>2315052@gndec.test</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -19896,7 +19896,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2315053@gndec.demo</t>
+          <t>2315053@gndec.test</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2315054@gndec.demo</t>
+          <t>2315054@gndec.test</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2315055@gndec.demo</t>
+          <t>2315055@gndec.test</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2315056@gndec.demo</t>
+          <t>2315056@gndec.test</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2315057@gndec.demo</t>
+          <t>2315057@gndec.test</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2315058@gndec.demo</t>
+          <t>2315058@gndec.test</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2315059@gndec.demo</t>
+          <t>2315059@gndec.test</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2315060@gndec.demo</t>
+          <t>2315060@gndec.test</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2315061@gndec.demo</t>
+          <t>2315061@gndec.test</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2315062@gndec.demo</t>
+          <t>2315062@gndec.test</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2315063@gndec.demo</t>
+          <t>2315063@gndec.test</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2315064@gndec.demo</t>
+          <t>2315064@gndec.test</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2315065@gndec.demo</t>
+          <t>2315065@gndec.test</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2315066@gndec.demo</t>
+          <t>2315066@gndec.test</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2315067@gndec.demo</t>
+          <t>2315067@gndec.test</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2315068@gndec.demo</t>
+          <t>2315068@gndec.test</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>2315069@gndec.demo</t>
+          <t>2315069@gndec.test</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2315070@gndec.demo</t>
+          <t>2315070@gndec.test</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>2315071@gndec.demo</t>
+          <t>2315071@gndec.test</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>2315072@gndec.demo</t>
+          <t>2315072@gndec.test</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>2315073@gndec.demo</t>
+          <t>2315073@gndec.test</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>2315074@gndec.demo</t>
+          <t>2315074@gndec.test</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>2315075@gndec.demo</t>
+          <t>2315075@gndec.test</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>2315076@gndec.demo</t>
+          <t>2315076@gndec.test</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>2315077@gndec.demo</t>
+          <t>2315077@gndec.test</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>2315078@gndec.demo</t>
+          <t>2315078@gndec.test</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2315079@gndec.demo</t>
+          <t>2315079@gndec.test</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>2315080@gndec.demo</t>
+          <t>2315080@gndec.test</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -20652,7 +20652,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>2315081@gndec.demo</t>
+          <t>2315081@gndec.test</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>2315082@gndec.demo</t>
+          <t>2315082@gndec.test</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -20706,7 +20706,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>2315083@gndec.demo</t>
+          <t>2315083@gndec.test</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>2315084@gndec.demo</t>
+          <t>2315084@gndec.test</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>2315085@gndec.demo</t>
+          <t>2315085@gndec.test</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>2315086@gndec.demo</t>
+          <t>2315086@gndec.test</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -20814,7 +20814,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>2315087@gndec.demo</t>
+          <t>2315087@gndec.test</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>2315088@gndec.demo</t>
+          <t>2315088@gndec.test</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>2315089@gndec.demo</t>
+          <t>2315089@gndec.test</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>2315090@gndec.demo</t>
+          <t>2315090@gndec.test</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>2315091@gndec.demo</t>
+          <t>2315091@gndec.test</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>2315092@gndec.demo</t>
+          <t>2315092@gndec.test</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>2315093@gndec.demo</t>
+          <t>2315093@gndec.test</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>2315094@gndec.demo</t>
+          <t>2315094@gndec.test</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>2315095@gndec.demo</t>
+          <t>2315095@gndec.test</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>2315096@gndec.demo</t>
+          <t>2315096@gndec.test</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>2315097@gndec.demo</t>
+          <t>2315097@gndec.test</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>2315098@gndec.demo</t>
+          <t>2315098@gndec.test</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>2315099@gndec.demo</t>
+          <t>2315099@gndec.test</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>2315100@gndec.demo</t>
+          <t>2315100@gndec.test</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -21192,7 +21192,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>2315101@gndec.demo</t>
+          <t>2315101@gndec.test</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>2315102@gndec.demo</t>
+          <t>2315102@gndec.test</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>2315103@gndec.demo</t>
+          <t>2315103@gndec.test</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>2315104@gndec.demo</t>
+          <t>2315104@gndec.test</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>2315105@gndec.demo</t>
+          <t>2315105@gndec.test</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>2315106@gndec.demo</t>
+          <t>2315106@gndec.test</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>2315107@gndec.demo</t>
+          <t>2315107@gndec.test</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>2315108@gndec.demo</t>
+          <t>2315108@gndec.test</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>2315109@gndec.demo</t>
+          <t>2315109@gndec.test</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>2315110@gndec.demo</t>
+          <t>2315110@gndec.test</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -21462,7 +21462,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>2315111@gndec.demo</t>
+          <t>2315111@gndec.test</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>2315112@gndec.demo</t>
+          <t>2315112@gndec.test</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2315113@gndec.demo</t>
+          <t>2315113@gndec.test</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2315114@gndec.demo</t>
+          <t>2315114@gndec.test</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -21570,7 +21570,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>2315115@gndec.demo</t>
+          <t>2315115@gndec.test</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>2315116@gndec.demo</t>
+          <t>2315116@gndec.test</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>2315117@gndec.demo</t>
+          <t>2315117@gndec.test</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>2315118@gndec.demo</t>
+          <t>2315118@gndec.test</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>2315119@gndec.demo</t>
+          <t>2315119@gndec.test</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>2315120@gndec.demo</t>
+          <t>2315120@gndec.test</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>2315121@gndec.demo</t>
+          <t>2315121@gndec.test</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>2315122@gndec.demo</t>
+          <t>2315122@gndec.test</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>2315123@gndec.demo</t>
+          <t>2315123@gndec.test</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>2315124@gndec.demo</t>
+          <t>2315124@gndec.test</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>2315125@gndec.demo</t>
+          <t>2315125@gndec.test</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -21867,7 +21867,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>2315126@gndec.demo</t>
+          <t>2315126@gndec.test</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>2315127@gndec.demo</t>
+          <t>2315127@gndec.test</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>2315128@gndec.demo</t>
+          <t>2315128@gndec.test</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>2315129@gndec.demo</t>
+          <t>2315129@gndec.test</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -21975,7 +21975,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>2315130@gndec.demo</t>
+          <t>2315130@gndec.test</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>2315131@gndec.demo</t>
+          <t>2315131@gndec.test</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>2315132@gndec.demo</t>
+          <t>2315132@gndec.test</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>2315133@gndec.demo</t>
+          <t>2315133@gndec.test</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>2315134@gndec.demo</t>
+          <t>2315134@gndec.test</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>2315135@gndec.demo</t>
+          <t>2315135@gndec.test</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>2315136@gndec.demo</t>
+          <t>2315136@gndec.test</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>2315137@gndec.demo</t>
+          <t>2315137@gndec.test</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>2315138@gndec.demo</t>
+          <t>2315138@gndec.test</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>2315139@gndec.demo</t>
+          <t>2315139@gndec.test</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>2315140@gndec.demo</t>
+          <t>2315140@gndec.test</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>2315141@gndec.demo</t>
+          <t>2315141@gndec.test</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>2315142@gndec.demo</t>
+          <t>2315142@gndec.test</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>2315143@gndec.demo</t>
+          <t>2315143@gndec.test</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>2315144@gndec.demo</t>
+          <t>2315144@gndec.test</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>2315145@gndec.demo</t>
+          <t>2315145@gndec.test</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>2315146@gndec.demo</t>
+          <t>2315146@gndec.test</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>2315147@gndec.demo</t>
+          <t>2315147@gndec.test</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>2315148@gndec.demo</t>
+          <t>2315148@gndec.test</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>2315149@gndec.demo</t>
+          <t>2315149@gndec.test</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -22515,7 +22515,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>2315150@gndec.demo</t>
+          <t>2315150@gndec.test</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>2315151@gndec.demo</t>
+          <t>2315151@gndec.test</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>2315152@gndec.demo</t>
+          <t>2315152@gndec.test</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>2315153@gndec.demo</t>
+          <t>2315153@gndec.test</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>2315154@gndec.demo</t>
+          <t>2315154@gndec.test</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>2315155@gndec.demo</t>
+          <t>2315155@gndec.test</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>2315156@gndec.demo</t>
+          <t>2315156@gndec.test</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>2315157@gndec.demo</t>
+          <t>2315157@gndec.test</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>2315158@gndec.demo</t>
+          <t>2315158@gndec.test</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>2315159@gndec.demo</t>
+          <t>2315159@gndec.test</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -22785,7 +22785,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>2315160@gndec.demo</t>
+          <t>2315160@gndec.test</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -22812,7 +22812,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>2315161@gndec.demo</t>
+          <t>2315161@gndec.test</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -22839,7 +22839,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>2315162@gndec.demo</t>
+          <t>2315162@gndec.test</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>2315163@gndec.demo</t>
+          <t>2315163@gndec.test</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>2315164@gndec.demo</t>
+          <t>2315164@gndec.test</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>2315165@gndec.demo</t>
+          <t>2315165@gndec.test</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>2315166@gndec.demo</t>
+          <t>2315166@gndec.test</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>2315167@gndec.demo</t>
+          <t>2315167@gndec.test</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>2315168@gndec.demo</t>
+          <t>2315168@gndec.test</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>2315169@gndec.demo</t>
+          <t>2315169@gndec.test</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>2315170@gndec.demo</t>
+          <t>2315170@gndec.test</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>2315171@gndec.demo</t>
+          <t>2315171@gndec.test</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>2315172@gndec.demo</t>
+          <t>2315172@gndec.test</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>2315173@gndec.demo</t>
+          <t>2315173@gndec.test</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>2315174@gndec.demo</t>
+          <t>2315174@gndec.test</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>2315175@gndec.demo</t>
+          <t>2315175@gndec.test</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>2315176@gndec.demo</t>
+          <t>2315176@gndec.test</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>2315177@gndec.demo</t>
+          <t>2315177@gndec.test</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>2315178@gndec.demo</t>
+          <t>2315178@gndec.test</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
